--- a/نات هيلث للتأمين.xlsx
+++ b/نات هيلث للتأمين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F1B504-1F0B-4EB0-82E6-7301220FD423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEE3765-E67E-4F59-BD6C-BC524A285706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1DC53A1F-76F9-410D-8A40-2032C97E1510}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="699">
   <si>
     <t>الرقم</t>
   </si>
@@ -2118,6 +2118,21 @@
   </si>
   <si>
     <t>فاطمة موسى عطالله  السعيدات</t>
+  </si>
+  <si>
+    <t>مرح خالد عيسى الحسنات</t>
+  </si>
+  <si>
+    <t>موسى يوسف موسى الحمادين</t>
+  </si>
+  <si>
+    <t>يوسف موسى عطية الحمادين</t>
+  </si>
+  <si>
+    <t>ينال يوسف موسى الحمادين</t>
+  </si>
+  <si>
+    <t>جود رائد الصبيحات</t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22865DC0-B890-4D8D-83EE-833A3F5E241E}">
-  <dimension ref="A1:L1479"/>
+  <dimension ref="A1:L1502"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -54409,7 +54424,7 @@
       </c>
       <c r="K1402"/>
       <c r="L1402" s="6">
-        <f t="shared" ref="L1402:L1454" si="44">J1402-K1402</f>
+        <f t="shared" ref="L1402:L1465" si="44">J1402-K1402</f>
         <v>20.999599999999997</v>
       </c>
     </row>
@@ -54746,7 +54761,7 @@
         <v>20.8</v>
       </c>
       <c r="J1411" s="6">
-        <f t="shared" ref="J1411:J1454" si="45">G1411*0.94-H1411</f>
+        <f t="shared" ref="J1411:J1474" si="45">G1411*0.94-H1411</f>
         <v>19.552</v>
       </c>
       <c r="K1411"/>
@@ -56346,764 +56361,1803 @@
       </c>
     </row>
     <row r="1455" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1455" s="8">
+      <c r="A1455" s="2">
         <v>1</v>
       </c>
-      <c r="B1455" s="8">
+      <c r="B1455" s="2">
         <v>9592022140</v>
       </c>
-      <c r="C1455" s="8" t="s">
+      <c r="C1455" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1455" s="8">
+      <c r="D1455" s="2">
         <v>959110220</v>
       </c>
-      <c r="E1455" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1455" s="9">
+      <c r="E1455" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1455" s="3">
         <v>46176</v>
       </c>
-      <c r="G1455" s="8">
+      <c r="G1455" s="2">
         <v>88.93</v>
       </c>
-      <c r="H1455" s="8">
+      <c r="H1455" s="2">
         <v>22.231999999999999</v>
       </c>
-      <c r="I1455" s="8">
+      <c r="I1455" s="2">
         <v>66.697999999999993</v>
       </c>
-      <c r="J1455" s="7"/>
-      <c r="K1455" s="7"/>
-      <c r="L1455" s="7"/>
+      <c r="J1455" s="6">
+        <f t="shared" si="45"/>
+        <v>61.362200000000001</v>
+      </c>
+      <c r="K1455"/>
+      <c r="L1455" s="6">
+        <f t="shared" si="44"/>
+        <v>61.362200000000001</v>
+      </c>
     </row>
     <row r="1456" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1456" s="8">
+      <c r="A1456" s="2">
         <v>2</v>
       </c>
-      <c r="B1456" s="8">
+      <c r="B1456" s="2">
         <v>2001435100</v>
       </c>
-      <c r="C1456" s="8" t="s">
+      <c r="C1456" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="D1456" s="8">
+      <c r="D1456" s="2">
         <v>20014525</v>
       </c>
-      <c r="E1456" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1456" s="9">
+      <c r="E1456" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1456" s="3">
         <v>46177</v>
       </c>
-      <c r="G1456" s="8">
+      <c r="G1456" s="2">
         <v>92.78</v>
       </c>
-      <c r="H1456" s="8">
+      <c r="H1456" s="2">
         <v>18.556000000000001</v>
       </c>
-      <c r="I1456" s="8">
+      <c r="I1456" s="2">
         <v>74.224000000000004</v>
       </c>
-      <c r="J1456" s="7"/>
-      <c r="K1456" s="7"/>
-      <c r="L1456" s="7"/>
+      <c r="J1456" s="6">
+        <f t="shared" si="45"/>
+        <v>68.657200000000003</v>
+      </c>
+      <c r="K1456"/>
+      <c r="L1456" s="6">
+        <f t="shared" si="44"/>
+        <v>68.657200000000003</v>
+      </c>
     </row>
     <row r="1457" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1457" s="8">
+      <c r="A1457" s="2">
         <v>3</v>
       </c>
-      <c r="B1457" s="8">
+      <c r="B1457" s="2">
         <v>9882000587</v>
       </c>
-      <c r="C1457" s="8" t="s">
+      <c r="C1457" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D1457" s="8">
+      <c r="D1457" s="2">
         <v>988200454</v>
       </c>
-      <c r="E1457" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1457" s="9">
+      <c r="E1457" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1457" s="3">
         <v>46180</v>
       </c>
-      <c r="G1457" s="8">
+      <c r="G1457" s="2">
         <v>42.9</v>
       </c>
-      <c r="H1457" s="8">
+      <c r="H1457" s="2">
         <v>0</v>
       </c>
-      <c r="I1457" s="8">
+      <c r="I1457" s="2">
         <v>42.9</v>
       </c>
-      <c r="J1457" s="7"/>
-      <c r="K1457" s="7"/>
-      <c r="L1457" s="7"/>
+      <c r="J1457" s="6">
+        <f t="shared" si="45"/>
+        <v>40.325999999999993</v>
+      </c>
+      <c r="K1457"/>
+      <c r="L1457" s="6">
+        <f t="shared" si="44"/>
+        <v>40.325999999999993</v>
+      </c>
     </row>
     <row r="1458" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1458" s="8">
+      <c r="A1458" s="2">
         <v>4</v>
       </c>
-      <c r="B1458" s="8">
+      <c r="B1458" s="2">
         <v>9552017225</v>
       </c>
-      <c r="C1458" s="8" t="s">
+      <c r="C1458" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D1458" s="8">
+      <c r="D1458" s="2">
         <v>9552012</v>
       </c>
-      <c r="E1458" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1458" s="9">
+      <c r="E1458" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1458" s="3">
         <v>46181</v>
       </c>
-      <c r="G1458" s="8">
+      <c r="G1458" s="2">
         <v>47.39</v>
       </c>
-      <c r="H1458" s="8">
+      <c r="H1458" s="2">
         <v>7.1079999999999997</v>
       </c>
-      <c r="I1458" s="8">
+      <c r="I1458" s="2">
         <v>40.281999999999996</v>
       </c>
-      <c r="J1458" s="7"/>
-      <c r="K1458" s="7"/>
-      <c r="L1458" s="7"/>
+      <c r="J1458" s="6">
+        <f t="shared" si="45"/>
+        <v>37.438600000000001</v>
+      </c>
+      <c r="K1458"/>
+      <c r="L1458" s="6">
+        <f t="shared" si="44"/>
+        <v>37.438600000000001</v>
+      </c>
     </row>
     <row r="1459" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1459" s="8">
+      <c r="A1459" s="2">
         <v>5</v>
       </c>
-      <c r="B1459" s="8">
+      <c r="B1459" s="2">
         <v>9672033899</v>
       </c>
-      <c r="C1459" s="8" t="s">
+      <c r="C1459" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D1459" s="8">
+      <c r="D1459" s="2">
         <v>202613979</v>
       </c>
-      <c r="E1459" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1459" s="9">
+      <c r="E1459" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1459" s="3">
         <v>46182</v>
       </c>
-      <c r="G1459" s="8">
+      <c r="G1459" s="2">
         <v>66.94</v>
       </c>
-      <c r="H1459" s="8">
+      <c r="H1459" s="2">
         <v>10.041</v>
       </c>
-      <c r="I1459" s="8">
+      <c r="I1459" s="2">
         <v>56.899000000000001</v>
       </c>
-      <c r="J1459" s="7"/>
-      <c r="K1459" s="7"/>
-      <c r="L1459" s="7"/>
+      <c r="J1459" s="6">
+        <f t="shared" si="45"/>
+        <v>52.882599999999996</v>
+      </c>
+      <c r="K1459"/>
+      <c r="L1459" s="6">
+        <f t="shared" si="44"/>
+        <v>52.882599999999996</v>
+      </c>
     </row>
     <row r="1460" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1460" s="8">
+      <c r="A1460" s="2">
         <v>6</v>
       </c>
-      <c r="B1460" s="8">
+      <c r="B1460" s="2">
         <v>9991062435</v>
       </c>
-      <c r="C1460" s="8" t="s">
+      <c r="C1460" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D1460" s="8">
+      <c r="D1460" s="2">
         <v>991062454</v>
       </c>
-      <c r="E1460" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1460" s="9">
+      <c r="E1460" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1460" s="3">
         <v>46183</v>
       </c>
-      <c r="G1460" s="8">
+      <c r="G1460" s="2">
         <v>30.62</v>
       </c>
-      <c r="H1460" s="8">
+      <c r="H1460" s="2">
         <v>0</v>
       </c>
-      <c r="I1460" s="8">
+      <c r="I1460" s="2">
         <v>30.62</v>
       </c>
-      <c r="J1460" s="7"/>
-      <c r="K1460" s="7"/>
-      <c r="L1460" s="7"/>
+      <c r="J1460" s="6">
+        <f t="shared" si="45"/>
+        <v>28.782799999999998</v>
+      </c>
+      <c r="K1460"/>
+      <c r="L1460" s="6">
+        <f t="shared" si="44"/>
+        <v>28.782799999999998</v>
+      </c>
     </row>
     <row r="1461" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1461" s="8">
+      <c r="A1461" s="2">
         <v>7</v>
       </c>
-      <c r="B1461" s="8">
+      <c r="B1461" s="2">
         <v>9771047773</v>
       </c>
-      <c r="C1461" s="8" t="s">
+      <c r="C1461" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D1461" s="8">
+      <c r="D1461" s="2">
         <v>9771011</v>
       </c>
-      <c r="E1461" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1461" s="9">
+      <c r="E1461" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1461" s="3">
         <v>46184</v>
       </c>
-      <c r="G1461" s="8">
+      <c r="G1461" s="2">
         <v>27.44</v>
       </c>
-      <c r="H1461" s="8">
+      <c r="H1461" s="2">
         <v>5.4880000000000004</v>
       </c>
-      <c r="I1461" s="8">
+      <c r="I1461" s="2">
         <v>21.952000000000002</v>
       </c>
-      <c r="J1461" s="7"/>
-      <c r="K1461" s="7"/>
-      <c r="L1461" s="7"/>
+      <c r="J1461" s="6">
+        <f t="shared" si="45"/>
+        <v>20.305600000000002</v>
+      </c>
+      <c r="K1461"/>
+      <c r="L1461" s="6">
+        <f t="shared" si="44"/>
+        <v>20.305600000000002</v>
+      </c>
     </row>
     <row r="1462" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1462" s="8">
+      <c r="A1462" s="2">
         <v>8</v>
       </c>
-      <c r="B1462" s="8">
+      <c r="B1462" s="2">
         <v>9531015239</v>
       </c>
-      <c r="C1462" s="8" t="s">
+      <c r="C1462" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D1462" s="8">
+      <c r="D1462" s="2">
         <v>202614264</v>
       </c>
-      <c r="E1462" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1462" s="9">
+      <c r="E1462" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1462" s="3">
         <v>46186</v>
       </c>
-      <c r="G1462" s="8">
+      <c r="G1462" s="2">
         <v>90.37</v>
       </c>
-      <c r="H1462" s="8">
+      <c r="H1462" s="2">
         <v>13.555</v>
       </c>
-      <c r="I1462" s="8">
+      <c r="I1462" s="2">
         <v>76.814999999999998</v>
       </c>
-      <c r="J1462" s="7"/>
-      <c r="K1462" s="7"/>
-      <c r="L1462" s="7"/>
+      <c r="J1462" s="6">
+        <f t="shared" si="45"/>
+        <v>71.392799999999994</v>
+      </c>
+      <c r="K1462"/>
+      <c r="L1462" s="6">
+        <f t="shared" si="44"/>
+        <v>71.392799999999994</v>
+      </c>
     </row>
     <row r="1463" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1463" s="8">
-        <v>9</v>
-      </c>
-      <c r="B1463" s="8">
+      <c r="A1463" s="2">
+        <v>9</v>
+      </c>
+      <c r="B1463" s="2">
         <v>40090462</v>
       </c>
-      <c r="C1463" s="8" t="s">
+      <c r="C1463" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="D1463" s="8">
+      <c r="D1463" s="2">
         <v>4009041</v>
       </c>
-      <c r="E1463" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1463" s="9">
+      <c r="E1463" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1463" s="3">
         <v>46186</v>
       </c>
-      <c r="G1463" s="8">
+      <c r="G1463" s="2">
         <v>59.48</v>
       </c>
-      <c r="H1463" s="8">
+      <c r="H1463" s="2">
         <v>0</v>
       </c>
-      <c r="I1463" s="8">
+      <c r="I1463" s="2">
         <v>59.48</v>
       </c>
-      <c r="J1463" s="7"/>
-      <c r="K1463" s="7"/>
-      <c r="L1463" s="7"/>
+      <c r="J1463" s="6">
+        <f t="shared" si="45"/>
+        <v>55.911199999999994</v>
+      </c>
+      <c r="K1463"/>
+      <c r="L1463" s="6">
+        <f t="shared" si="44"/>
+        <v>55.911199999999994</v>
+      </c>
     </row>
     <row r="1464" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1464" s="8">
+      <c r="A1464" s="2">
         <v>10</v>
       </c>
-      <c r="B1464" s="8">
+      <c r="B1464" s="2">
         <v>9672033899</v>
       </c>
-      <c r="C1464" s="8" t="s">
+      <c r="C1464" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D1464" s="8">
+      <c r="D1464" s="2">
         <v>9672013</v>
       </c>
-      <c r="E1464" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1464" s="9">
+      <c r="E1464" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1464" s="3">
         <v>46186</v>
       </c>
-      <c r="G1464" s="8">
+      <c r="G1464" s="2">
         <v>69.89</v>
       </c>
-      <c r="H1464" s="8">
+      <c r="H1464" s="2">
         <v>10.483000000000001</v>
       </c>
-      <c r="I1464" s="8">
+      <c r="I1464" s="2">
         <v>59.406999999999996</v>
       </c>
-      <c r="J1464" s="7"/>
-      <c r="K1464" s="7"/>
-      <c r="L1464" s="7"/>
+      <c r="J1464" s="6">
+        <f t="shared" si="45"/>
+        <v>55.2136</v>
+      </c>
+      <c r="K1464"/>
+      <c r="L1464" s="6">
+        <f t="shared" si="44"/>
+        <v>55.2136</v>
+      </c>
     </row>
     <row r="1465" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1465" s="8">
-        <v>11</v>
-      </c>
-      <c r="B1465" s="8">
+      <c r="A1465" s="2">
+        <v>11</v>
+      </c>
+      <c r="B1465" s="2">
         <v>9732046944</v>
       </c>
-      <c r="C1465" s="8" t="s">
+      <c r="C1465" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D1465" s="8">
+      <c r="D1465" s="2">
         <v>202614357</v>
       </c>
-      <c r="E1465" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1465" s="9">
+      <c r="E1465" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1465" s="3">
         <v>46187</v>
       </c>
-      <c r="G1465" s="8">
+      <c r="G1465" s="2">
         <v>65.58</v>
       </c>
-      <c r="H1465" s="8">
+      <c r="H1465" s="2">
         <v>9.8369999999999997</v>
       </c>
-      <c r="I1465" s="8">
+      <c r="I1465" s="2">
         <v>55.743000000000002</v>
       </c>
-      <c r="J1465" s="7"/>
-      <c r="K1465" s="7"/>
-      <c r="L1465" s="7"/>
+      <c r="J1465" s="6">
+        <f t="shared" si="45"/>
+        <v>51.808199999999999</v>
+      </c>
+      <c r="K1465"/>
+      <c r="L1465" s="6">
+        <f t="shared" si="44"/>
+        <v>51.808199999999999</v>
+      </c>
     </row>
     <row r="1466" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1466" s="8">
+      <c r="A1466" s="2">
         <v>12</v>
       </c>
-      <c r="B1466" s="8">
+      <c r="B1466" s="2">
         <v>9931061185</v>
       </c>
-      <c r="C1466" s="8" t="s">
+      <c r="C1466" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D1466" s="8">
+      <c r="D1466" s="2">
         <v>202614435</v>
       </c>
-      <c r="E1466" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1466" s="9">
+      <c r="E1466" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1466" s="3">
         <v>46188</v>
       </c>
-      <c r="G1466" s="8">
+      <c r="G1466" s="2">
         <v>32.729999999999997</v>
       </c>
-      <c r="H1466" s="8">
+      <c r="H1466" s="2">
         <v>4.9089999999999998</v>
       </c>
-      <c r="I1466" s="8">
+      <c r="I1466" s="2">
         <v>27.821000000000002</v>
       </c>
-      <c r="J1466" s="7"/>
-      <c r="K1466" s="7"/>
-      <c r="L1466" s="7"/>
+      <c r="J1466" s="6">
+        <f t="shared" si="45"/>
+        <v>25.857199999999995</v>
+      </c>
+      <c r="K1466"/>
+      <c r="L1466" s="6">
+        <f t="shared" ref="L1466:L1502" si="46">J1466-K1466</f>
+        <v>25.857199999999995</v>
+      </c>
     </row>
     <row r="1467" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1467" s="8">
+      <c r="A1467" s="2">
         <v>13</v>
       </c>
-      <c r="B1467" s="8">
+      <c r="B1467" s="2">
         <v>9572020006</v>
       </c>
-      <c r="C1467" s="8" t="s">
+      <c r="C1467" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D1467" s="8">
+      <c r="D1467" s="2">
         <v>202614547</v>
       </c>
-      <c r="E1467" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1467" s="9">
+      <c r="E1467" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1467" s="3">
         <v>46190</v>
       </c>
-      <c r="G1467" s="8">
+      <c r="G1467" s="2">
         <v>71.400000000000006</v>
       </c>
-      <c r="H1467" s="8">
+      <c r="H1467" s="2">
         <v>17.850000000000001</v>
       </c>
-      <c r="I1467" s="8">
+      <c r="I1467" s="2">
         <v>53.55</v>
       </c>
+      <c r="J1467" s="6">
+        <f t="shared" si="45"/>
+        <v>49.265999999999998</v>
+      </c>
+      <c r="L1467" s="6">
+        <f t="shared" si="46"/>
+        <v>49.265999999999998</v>
+      </c>
     </row>
     <row r="1468" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1468" s="8">
+      <c r="A1468" s="2">
         <v>14</v>
       </c>
-      <c r="B1468" s="8">
+      <c r="B1468" s="2">
         <v>2004501108</v>
       </c>
-      <c r="C1468" s="8" t="s">
+      <c r="C1468" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D1468" s="8">
+      <c r="D1468" s="2">
         <v>202614560</v>
       </c>
-      <c r="E1468" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1468" s="9">
+      <c r="E1468" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1468" s="3">
         <v>46190</v>
       </c>
-      <c r="G1468" s="8">
+      <c r="G1468" s="2">
         <v>13.77</v>
       </c>
-      <c r="H1468" s="8">
+      <c r="H1468" s="2">
         <v>0</v>
       </c>
-      <c r="I1468" s="8">
+      <c r="I1468" s="2">
         <v>13.77</v>
       </c>
+      <c r="J1468" s="6">
+        <f t="shared" si="45"/>
+        <v>12.9438</v>
+      </c>
+      <c r="L1468" s="6">
+        <f t="shared" si="46"/>
+        <v>12.9438</v>
+      </c>
     </row>
     <row r="1469" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1469" s="8">
+      <c r="A1469" s="2">
         <v>15</v>
       </c>
-      <c r="B1469" s="8">
+      <c r="B1469" s="2">
         <v>40220569</v>
       </c>
-      <c r="C1469" s="8" t="s">
+      <c r="C1469" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="D1469" s="8">
+      <c r="D1469" s="2">
         <v>4022022</v>
       </c>
-      <c r="E1469" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1469" s="9">
+      <c r="E1469" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1469" s="3">
         <v>46190</v>
       </c>
-      <c r="G1469" s="8">
+      <c r="G1469" s="2">
         <v>34.700000000000003</v>
       </c>
-      <c r="H1469" s="8">
+      <c r="H1469" s="2">
         <v>4.1639999999999997</v>
       </c>
-      <c r="I1469" s="8">
+      <c r="I1469" s="2">
         <v>30.536000000000001</v>
       </c>
+      <c r="J1469" s="6">
+        <f t="shared" si="45"/>
+        <v>28.454000000000001</v>
+      </c>
+      <c r="L1469" s="6">
+        <f t="shared" si="46"/>
+        <v>28.454000000000001</v>
+      </c>
     </row>
     <row r="1470" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1470" s="8">
+      <c r="A1470" s="2">
         <v>16</v>
       </c>
-      <c r="B1470" s="8">
+      <c r="B1470" s="2">
         <v>9602026931</v>
       </c>
-      <c r="C1470" s="8" t="s">
+      <c r="C1470" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1470" s="8">
+      <c r="D1470" s="2">
         <v>202614754</v>
       </c>
-      <c r="E1470" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1470" s="9">
+      <c r="E1470" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1470" s="3">
         <v>46193</v>
       </c>
-      <c r="G1470" s="8">
+      <c r="G1470" s="2">
         <v>71.239999999999995</v>
       </c>
-      <c r="H1470" s="8">
+      <c r="H1470" s="2">
         <v>10.686</v>
       </c>
-      <c r="I1470" s="8">
+      <c r="I1470" s="2">
         <v>60.554000000000002</v>
       </c>
+      <c r="J1470" s="6">
+        <f t="shared" si="45"/>
+        <v>56.279599999999995</v>
+      </c>
+      <c r="L1470" s="6">
+        <f t="shared" si="46"/>
+        <v>56.279599999999995</v>
+      </c>
     </row>
     <row r="1471" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1471" s="8">
+      <c r="A1471" s="2">
         <v>17</v>
       </c>
-      <c r="B1471" s="8">
+      <c r="B1471" s="2">
         <v>9981042468</v>
       </c>
-      <c r="C1471" s="8" t="s">
+      <c r="C1471" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="D1471" s="8">
+      <c r="D1471" s="2">
         <v>998101212</v>
       </c>
-      <c r="E1471" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1471" s="9">
+      <c r="E1471" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1471" s="3">
         <v>46193</v>
       </c>
-      <c r="G1471" s="8">
+      <c r="G1471" s="2">
         <v>34.31</v>
       </c>
-      <c r="H1471" s="8">
+      <c r="H1471" s="2">
         <v>0</v>
       </c>
-      <c r="I1471" s="8">
+      <c r="I1471" s="2">
         <v>34.31</v>
       </c>
+      <c r="J1471" s="6">
+        <f t="shared" si="45"/>
+        <v>32.251400000000004</v>
+      </c>
+      <c r="L1471" s="6">
+        <f t="shared" si="46"/>
+        <v>32.251400000000004</v>
+      </c>
     </row>
     <row r="1472" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1472" s="8">
+      <c r="A1472" s="2">
         <v>18</v>
       </c>
-      <c r="B1472" s="8">
+      <c r="B1472" s="2">
         <v>9552017225</v>
       </c>
-      <c r="C1472" s="8" t="s">
+      <c r="C1472" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D1472" s="8">
+      <c r="D1472" s="2">
         <v>202614912</v>
       </c>
-      <c r="E1472" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1472" s="9">
+      <c r="E1472" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1472" s="3">
         <v>46195</v>
       </c>
-      <c r="G1472" s="8">
+      <c r="G1472" s="2">
         <v>25.23</v>
       </c>
-      <c r="H1472" s="8">
+      <c r="H1472" s="2">
         <v>3.7839999999999998</v>
       </c>
-      <c r="I1472" s="8">
+      <c r="I1472" s="2">
         <v>21.446000000000002</v>
       </c>
-    </row>
-    <row r="1473" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1473" s="8">
+      <c r="J1472" s="6">
+        <f t="shared" si="45"/>
+        <v>19.932200000000002</v>
+      </c>
+      <c r="L1472" s="6">
+        <f t="shared" si="46"/>
+        <v>19.932200000000002</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1473" s="2">
         <v>19</v>
       </c>
-      <c r="B1473" s="8">
+      <c r="B1473" s="2">
         <v>2002090051</v>
       </c>
-      <c r="C1473" s="8" t="s">
+      <c r="C1473" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="D1473" s="8">
+      <c r="D1473" s="2">
         <v>20020955</v>
       </c>
-      <c r="E1473" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1473" s="9">
+      <c r="E1473" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1473" s="3">
         <v>46195</v>
       </c>
-      <c r="G1473" s="8">
+      <c r="G1473" s="2">
         <v>2.2400000000000002</v>
       </c>
-      <c r="H1473" s="8">
+      <c r="H1473" s="2">
         <v>0.224</v>
       </c>
-      <c r="I1473" s="8">
+      <c r="I1473" s="2">
         <v>2.016</v>
       </c>
-    </row>
-    <row r="1474" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1474" s="8">
+      <c r="J1473" s="6">
+        <f t="shared" si="45"/>
+        <v>1.8815999999999999</v>
+      </c>
+      <c r="L1473" s="6">
+        <f t="shared" si="46"/>
+        <v>1.8815999999999999</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1474" s="2">
         <v>20</v>
       </c>
-      <c r="B1474" s="8">
+      <c r="B1474" s="2">
         <v>40087408</v>
       </c>
-      <c r="C1474" s="8" t="s">
+      <c r="C1474" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D1474" s="8">
+      <c r="D1474" s="2">
         <v>202615329</v>
       </c>
-      <c r="E1474" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1474" s="9">
+      <c r="E1474" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1474" s="3">
         <v>46201</v>
       </c>
-      <c r="G1474" s="8">
+      <c r="G1474" s="2">
         <v>49.44</v>
       </c>
-      <c r="H1474" s="8">
+      <c r="H1474" s="2">
         <v>0</v>
       </c>
-      <c r="I1474" s="8">
+      <c r="I1474" s="2">
         <v>49.44</v>
       </c>
-    </row>
-    <row r="1475" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1475" s="8">
+      <c r="J1474" s="6">
+        <f t="shared" si="45"/>
+        <v>46.473599999999998</v>
+      </c>
+      <c r="L1474" s="6">
+        <f t="shared" si="46"/>
+        <v>46.473599999999998</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1475" s="2">
         <v>21</v>
       </c>
-      <c r="B1475" s="8">
+      <c r="B1475" s="2">
         <v>2001832285</v>
       </c>
-      <c r="C1475" s="8" t="s">
+      <c r="C1475" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D1475" s="8">
+      <c r="D1475" s="2">
         <v>202615351</v>
       </c>
-      <c r="E1475" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1475" s="9">
+      <c r="E1475" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1475" s="3">
         <v>46201</v>
       </c>
-      <c r="G1475" s="8">
+      <c r="G1475" s="2">
         <v>23.138000000000002</v>
       </c>
-      <c r="H1475" s="8">
+      <c r="H1475" s="2">
         <v>2.3140000000000001</v>
       </c>
-      <c r="I1475" s="8">
+      <c r="I1475" s="2">
         <v>20.824000000000002</v>
       </c>
-    </row>
-    <row r="1476" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1476" s="8">
+      <c r="J1475" s="6">
+        <f t="shared" ref="J1475:J1502" si="47">G1475*0.94-H1475</f>
+        <v>19.43572</v>
+      </c>
+      <c r="L1475" s="6">
+        <f t="shared" si="46"/>
+        <v>19.43572</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1476" s="2">
         <v>22</v>
       </c>
-      <c r="B1476" s="8">
+      <c r="B1476" s="2">
         <v>2001483736</v>
       </c>
-      <c r="C1476" s="8" t="s">
+      <c r="C1476" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="D1476" s="8">
+      <c r="D1476" s="2">
         <v>202615352</v>
       </c>
-      <c r="E1476" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1476" s="9">
+      <c r="E1476" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1476" s="3">
         <v>46201</v>
       </c>
-      <c r="G1476" s="8">
+      <c r="G1476" s="2">
         <v>16.649999999999999</v>
       </c>
-      <c r="H1476" s="8">
+      <c r="H1476" s="2">
         <v>1.665</v>
       </c>
-      <c r="I1476" s="8">
+      <c r="I1476" s="2">
         <v>14.984999999999999</v>
       </c>
-    </row>
-    <row r="1477" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1477" s="8">
+      <c r="J1476" s="6">
+        <f t="shared" si="47"/>
+        <v>13.985999999999997</v>
+      </c>
+      <c r="L1476" s="6">
+        <f t="shared" si="46"/>
+        <v>13.985999999999997</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1477" s="2">
         <v>23</v>
       </c>
-      <c r="B1477" s="8">
+      <c r="B1477" s="2">
         <v>2000964572</v>
       </c>
-      <c r="C1477" s="8" t="s">
+      <c r="C1477" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D1477" s="8">
+      <c r="D1477" s="2">
         <v>202615353</v>
       </c>
-      <c r="E1477" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1477" s="9">
+      <c r="E1477" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1477" s="3">
         <v>46201</v>
       </c>
-      <c r="G1477" s="8">
+      <c r="G1477" s="2">
         <v>23.51</v>
       </c>
-      <c r="H1477" s="8">
+      <c r="H1477" s="2">
         <v>2.351</v>
       </c>
-      <c r="I1477" s="8">
+      <c r="I1477" s="2">
         <v>21.158999999999999</v>
       </c>
-    </row>
-    <row r="1478" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1478" s="8">
+      <c r="J1477" s="6">
+        <f t="shared" si="47"/>
+        <v>19.7484</v>
+      </c>
+      <c r="L1477" s="6">
+        <f t="shared" si="46"/>
+        <v>19.7484</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1478" s="2">
         <v>24</v>
       </c>
-      <c r="B1478" s="8">
+      <c r="B1478" s="2">
         <v>40220568</v>
       </c>
-      <c r="C1478" s="8" t="s">
+      <c r="C1478" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D1478" s="8">
+      <c r="D1478" s="2">
         <v>202615502</v>
       </c>
-      <c r="E1478" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1478" s="9">
+      <c r="E1478" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1478" s="3">
         <v>46203</v>
       </c>
-      <c r="G1478" s="8">
+      <c r="G1478" s="2">
         <v>39.520000000000003</v>
       </c>
-      <c r="H1478" s="8">
+      <c r="H1478" s="2">
         <v>3.952</v>
       </c>
-      <c r="I1478" s="8">
+      <c r="I1478" s="2">
         <v>35.567999999999998</v>
       </c>
-    </row>
-    <row r="1479" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1479" s="8">
+      <c r="J1478" s="6">
+        <f t="shared" si="47"/>
+        <v>33.196800000000003</v>
+      </c>
+      <c r="L1478" s="6">
+        <f t="shared" si="46"/>
+        <v>33.196800000000003</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1479" s="2">
         <v>25</v>
       </c>
-      <c r="B1479" s="8">
+      <c r="B1479" s="2">
         <v>40086774</v>
       </c>
-      <c r="C1479" s="8" t="s">
+      <c r="C1479" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D1479" s="8">
+      <c r="D1479" s="2">
         <v>202615529</v>
       </c>
-      <c r="E1479" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1479" s="9">
+      <c r="E1479" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1479" s="3">
         <v>46203</v>
       </c>
-      <c r="G1479" s="8">
+      <c r="G1479" s="2">
         <v>19.39</v>
       </c>
-      <c r="H1479" s="8">
+      <c r="H1479" s="2">
         <v>4.8470000000000004</v>
       </c>
-      <c r="I1479" s="8">
+      <c r="I1479" s="2">
         <v>14.542999999999999</v>
+      </c>
+      <c r="J1479" s="6">
+        <f t="shared" si="47"/>
+        <v>13.3796</v>
+      </c>
+      <c r="L1479" s="6">
+        <f t="shared" si="46"/>
+        <v>13.3796</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1480" s="8">
+        <v>1</v>
+      </c>
+      <c r="B1480" s="8">
+        <v>9592022140</v>
+      </c>
+      <c r="C1480" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1480" s="8">
+        <v>596545</v>
+      </c>
+      <c r="E1480" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1480" s="9">
+        <v>46205</v>
+      </c>
+      <c r="G1480" s="8">
+        <v>95.74</v>
+      </c>
+      <c r="H1480" s="8">
+        <v>23.934999999999999</v>
+      </c>
+      <c r="I1480" s="8">
+        <v>71.805000000000007</v>
+      </c>
+      <c r="J1480" s="6">
+        <f t="shared" si="47"/>
+        <v>66.060599999999994</v>
+      </c>
+      <c r="K1480" s="7"/>
+      <c r="L1480" s="6">
+        <f t="shared" si="46"/>
+        <v>66.060599999999994</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1481" s="8">
+        <v>2</v>
+      </c>
+      <c r="B1481" s="8">
+        <v>9991062435</v>
+      </c>
+      <c r="C1481" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D1481" s="8">
+        <v>202615788</v>
+      </c>
+      <c r="E1481" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1481" s="9">
+        <v>46207</v>
+      </c>
+      <c r="G1481" s="8">
+        <v>7.25</v>
+      </c>
+      <c r="H1481" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1481" s="8">
+        <v>7.25</v>
+      </c>
+      <c r="J1481" s="6">
+        <f t="shared" si="47"/>
+        <v>6.8149999999999995</v>
+      </c>
+      <c r="K1481" s="7"/>
+      <c r="L1481" s="6">
+        <f t="shared" si="46"/>
+        <v>6.8149999999999995</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1482" s="8">
+        <v>3</v>
+      </c>
+      <c r="B1482" s="8">
+        <v>40088621</v>
+      </c>
+      <c r="C1482" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="D1482" s="8">
+        <v>202615789</v>
+      </c>
+      <c r="E1482" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1482" s="9">
+        <v>46207</v>
+      </c>
+      <c r="G1482" s="8">
+        <v>13.75</v>
+      </c>
+      <c r="H1482" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1482" s="8">
+        <v>13.75</v>
+      </c>
+      <c r="J1482" s="6">
+        <f t="shared" si="47"/>
+        <v>12.924999999999999</v>
+      </c>
+      <c r="K1482" s="7"/>
+      <c r="L1482" s="6">
+        <f t="shared" si="46"/>
+        <v>12.924999999999999</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1483" s="8">
+        <v>4</v>
+      </c>
+      <c r="B1483" s="8">
+        <v>9001158701</v>
+      </c>
+      <c r="C1483" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="D1483" s="8">
+        <v>9001157</v>
+      </c>
+      <c r="E1483" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1483" s="9">
+        <v>46211</v>
+      </c>
+      <c r="G1483" s="8">
+        <v>21.65</v>
+      </c>
+      <c r="H1483" s="8">
+        <v>6.4950000000000001</v>
+      </c>
+      <c r="I1483" s="8">
+        <v>15.154999999999999</v>
+      </c>
+      <c r="J1483" s="6">
+        <f t="shared" si="47"/>
+        <v>13.855999999999998</v>
+      </c>
+      <c r="K1483" s="7"/>
+      <c r="L1483" s="6">
+        <f t="shared" si="46"/>
+        <v>13.855999999999998</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1484" s="8">
+        <v>5</v>
+      </c>
+      <c r="B1484" s="8">
+        <v>9531015239</v>
+      </c>
+      <c r="C1484" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1484" s="8">
+        <v>202616177</v>
+      </c>
+      <c r="E1484" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1484" s="9">
+        <v>46212</v>
+      </c>
+      <c r="G1484" s="8">
+        <v>86.58</v>
+      </c>
+      <c r="H1484" s="8">
+        <v>12.987</v>
+      </c>
+      <c r="I1484" s="8">
+        <v>73.593000000000004</v>
+      </c>
+      <c r="J1484" s="6">
+        <f t="shared" si="47"/>
+        <v>68.398200000000003</v>
+      </c>
+      <c r="K1484" s="7"/>
+      <c r="L1484" s="6">
+        <f t="shared" si="46"/>
+        <v>68.398200000000003</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1485" s="8">
+        <v>6</v>
+      </c>
+      <c r="B1485" s="8">
+        <v>2004143124</v>
+      </c>
+      <c r="C1485" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="D1485" s="8">
+        <v>202616385</v>
+      </c>
+      <c r="E1485" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1485" s="9">
+        <v>46214</v>
+      </c>
+      <c r="G1485" s="8">
+        <v>23.75</v>
+      </c>
+      <c r="H1485" s="8">
+        <v>3.5619999999999998</v>
+      </c>
+      <c r="I1485" s="8">
+        <v>20.187999999999999</v>
+      </c>
+      <c r="J1485" s="6">
+        <f t="shared" si="47"/>
+        <v>18.762999999999998</v>
+      </c>
+      <c r="K1485" s="7"/>
+      <c r="L1485" s="6">
+        <f t="shared" si="46"/>
+        <v>18.762999999999998</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1486" s="8">
+        <v>7</v>
+      </c>
+      <c r="B1486" s="8">
+        <v>9861028995</v>
+      </c>
+      <c r="C1486" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="D1486" s="8">
+        <v>202616386</v>
+      </c>
+      <c r="E1486" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1486" s="9">
+        <v>46214</v>
+      </c>
+      <c r="G1486" s="8">
+        <v>19.72</v>
+      </c>
+      <c r="H1486" s="8">
+        <v>2.9580000000000002</v>
+      </c>
+      <c r="I1486" s="8">
+        <v>16.762</v>
+      </c>
+      <c r="J1486" s="6">
+        <f t="shared" si="47"/>
+        <v>15.578799999999999</v>
+      </c>
+      <c r="K1486" s="7"/>
+      <c r="L1486" s="6">
+        <f t="shared" si="46"/>
+        <v>15.578799999999999</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1487" s="8">
+        <v>8</v>
+      </c>
+      <c r="B1487" s="8">
+        <v>2003171719</v>
+      </c>
+      <c r="C1487" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="D1487" s="8">
+        <v>202616387</v>
+      </c>
+      <c r="E1487" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1487" s="9">
+        <v>46214</v>
+      </c>
+      <c r="G1487" s="8">
+        <v>13.51</v>
+      </c>
+      <c r="H1487" s="8">
+        <v>2.0259999999999998</v>
+      </c>
+      <c r="I1487" s="8">
+        <v>11.484</v>
+      </c>
+      <c r="J1487" s="6">
+        <f t="shared" si="47"/>
+        <v>10.673399999999999</v>
+      </c>
+      <c r="K1487" s="7"/>
+      <c r="L1487" s="6">
+        <f t="shared" si="46"/>
+        <v>10.673399999999999</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1488" s="8">
+        <v>9</v>
+      </c>
+      <c r="B1488" s="8">
+        <v>200439018</v>
+      </c>
+      <c r="C1488" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1488" s="8">
+        <v>202616388</v>
+      </c>
+      <c r="E1488" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1488" s="9">
+        <v>46214</v>
+      </c>
+      <c r="G1488" s="8">
+        <v>48.07</v>
+      </c>
+      <c r="H1488" s="8">
+        <v>7.21</v>
+      </c>
+      <c r="I1488" s="8">
+        <v>40.86</v>
+      </c>
+      <c r="J1488" s="6">
+        <f t="shared" si="47"/>
+        <v>37.9758</v>
+      </c>
+      <c r="K1488" s="7"/>
+      <c r="L1488" s="6">
+        <f t="shared" si="46"/>
+        <v>37.9758</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1489" s="8">
+        <v>10</v>
+      </c>
+      <c r="B1489" s="8">
+        <v>9662041156</v>
+      </c>
+      <c r="C1489" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1489" s="8">
+        <v>96620414</v>
+      </c>
+      <c r="E1489" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1489" s="9">
+        <v>46214</v>
+      </c>
+      <c r="G1489" s="8">
+        <v>56.21</v>
+      </c>
+      <c r="H1489" s="8">
+        <v>11.242000000000001</v>
+      </c>
+      <c r="I1489" s="8">
+        <v>44.968000000000004</v>
+      </c>
+      <c r="J1489" s="6">
+        <f t="shared" si="47"/>
+        <v>41.595399999999998</v>
+      </c>
+      <c r="K1489" s="7"/>
+      <c r="L1489" s="6">
+        <f t="shared" si="46"/>
+        <v>41.595399999999998</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1490" s="8">
+        <v>11</v>
+      </c>
+      <c r="B1490" s="8">
+        <v>40220569</v>
+      </c>
+      <c r="C1490" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1490" s="8">
+        <v>202616500</v>
+      </c>
+      <c r="E1490" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1490" s="9">
+        <v>46215</v>
+      </c>
+      <c r="G1490" s="8">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="H1490" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="I1490" s="8">
+        <v>31.23</v>
+      </c>
+      <c r="J1490" s="6">
+        <f t="shared" si="47"/>
+        <v>29.148000000000003</v>
+      </c>
+      <c r="K1490" s="7"/>
+      <c r="L1490" s="6">
+        <f t="shared" si="46"/>
+        <v>29.148000000000003</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1491" s="8">
+        <v>12</v>
+      </c>
+      <c r="B1491" s="8">
+        <v>40087410</v>
+      </c>
+      <c r="C1491" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D1491" s="8">
+        <v>4008411</v>
+      </c>
+      <c r="E1491" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1491" s="9">
+        <v>46218</v>
+      </c>
+      <c r="G1491" s="8">
+        <v>53.9</v>
+      </c>
+      <c r="H1491" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1491" s="8">
+        <v>53.9</v>
+      </c>
+      <c r="J1491" s="6">
+        <f t="shared" si="47"/>
+        <v>50.665999999999997</v>
+      </c>
+      <c r="K1491" s="7"/>
+      <c r="L1491" s="6">
+        <f t="shared" si="46"/>
+        <v>50.665999999999997</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1492" s="8">
+        <v>13</v>
+      </c>
+      <c r="B1492" s="8">
+        <v>9572020006</v>
+      </c>
+      <c r="C1492" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1492" s="8">
+        <v>9572021212</v>
+      </c>
+      <c r="E1492" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1492" s="9">
+        <v>46219</v>
+      </c>
+      <c r="G1492" s="8">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="H1492" s="8">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="I1492" s="8">
+        <v>53.55</v>
+      </c>
+      <c r="J1492" s="6">
+        <f t="shared" si="47"/>
+        <v>49.265999999999998</v>
+      </c>
+      <c r="L1492" s="6">
+        <f t="shared" si="46"/>
+        <v>49.265999999999998</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1493" s="8">
+        <v>14</v>
+      </c>
+      <c r="B1493" s="8">
+        <v>9851047616</v>
+      </c>
+      <c r="C1493" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1493" s="8">
+        <v>202616916</v>
+      </c>
+      <c r="E1493" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1493" s="9">
+        <v>46221</v>
+      </c>
+      <c r="G1493" s="8">
+        <v>52.84</v>
+      </c>
+      <c r="H1493" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1493" s="8">
+        <v>52.84</v>
+      </c>
+      <c r="J1493" s="6">
+        <f t="shared" si="47"/>
+        <v>49.669600000000003</v>
+      </c>
+      <c r="L1493" s="6">
+        <f t="shared" si="46"/>
+        <v>49.669600000000003</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1494" s="8">
+        <v>15</v>
+      </c>
+      <c r="B1494" s="8">
+        <v>2004423187</v>
+      </c>
+      <c r="C1494" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="D1494" s="8">
+        <v>202616917</v>
+      </c>
+      <c r="E1494" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1494" s="9">
+        <v>46221</v>
+      </c>
+      <c r="G1494" s="8">
+        <v>24.46</v>
+      </c>
+      <c r="H1494" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1494" s="8">
+        <v>24.46</v>
+      </c>
+      <c r="J1494" s="6">
+        <f t="shared" si="47"/>
+        <v>22.9924</v>
+      </c>
+      <c r="L1494" s="6">
+        <f t="shared" si="46"/>
+        <v>22.9924</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1495" s="8">
+        <v>16</v>
+      </c>
+      <c r="B1495" s="8">
+        <v>9552017225</v>
+      </c>
+      <c r="C1495" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1495" s="8">
+        <v>17225</v>
+      </c>
+      <c r="E1495" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1495" s="9">
+        <v>46223</v>
+      </c>
+      <c r="G1495" s="8">
+        <v>25.11</v>
+      </c>
+      <c r="H1495" s="8">
+        <v>3.766</v>
+      </c>
+      <c r="I1495" s="8">
+        <v>21.344000000000001</v>
+      </c>
+      <c r="J1495" s="6">
+        <f t="shared" si="47"/>
+        <v>19.837399999999995</v>
+      </c>
+      <c r="L1495" s="6">
+        <f t="shared" si="46"/>
+        <v>19.837399999999995</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1496" s="8">
+        <v>17</v>
+      </c>
+      <c r="B1496" s="8">
+        <v>9771047773</v>
+      </c>
+      <c r="C1496" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1496" s="8">
+        <v>1047773</v>
+      </c>
+      <c r="E1496" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1496" s="9">
+        <v>46223</v>
+      </c>
+      <c r="G1496" s="8">
+        <v>38.31</v>
+      </c>
+      <c r="H1496" s="8">
+        <v>7.6619999999999999</v>
+      </c>
+      <c r="I1496" s="8">
+        <v>30.648</v>
+      </c>
+      <c r="J1496" s="6">
+        <f t="shared" si="47"/>
+        <v>28.349400000000003</v>
+      </c>
+      <c r="L1496" s="6">
+        <f t="shared" si="46"/>
+        <v>28.349400000000003</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1497" s="8">
+        <v>18</v>
+      </c>
+      <c r="B1497" s="8">
+        <v>9602026931</v>
+      </c>
+      <c r="C1497" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1497" s="8">
+        <v>202617181</v>
+      </c>
+      <c r="E1497" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1497" s="9">
+        <v>46224</v>
+      </c>
+      <c r="G1497" s="8">
+        <v>71.239999999999995</v>
+      </c>
+      <c r="H1497" s="8">
+        <v>10.686</v>
+      </c>
+      <c r="I1497" s="8">
+        <v>60.554000000000002</v>
+      </c>
+      <c r="J1497" s="6">
+        <f t="shared" si="47"/>
+        <v>56.279599999999995</v>
+      </c>
+      <c r="L1497" s="6">
+        <f t="shared" si="46"/>
+        <v>56.279599999999995</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1498" s="8">
+        <v>19</v>
+      </c>
+      <c r="B1498" s="8">
+        <v>40089015</v>
+      </c>
+      <c r="C1498" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1498" s="8">
+        <v>4008945</v>
+      </c>
+      <c r="E1498" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1498" s="9">
+        <v>46228</v>
+      </c>
+      <c r="G1498" s="8">
+        <v>46.17</v>
+      </c>
+      <c r="H1498" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1498" s="8">
+        <v>46.17</v>
+      </c>
+      <c r="J1498" s="6">
+        <f t="shared" si="47"/>
+        <v>43.399799999999999</v>
+      </c>
+      <c r="L1498" s="6">
+        <f t="shared" si="46"/>
+        <v>43.399799999999999</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1499" s="8">
+        <v>20</v>
+      </c>
+      <c r="B1499" s="8">
+        <v>40089016</v>
+      </c>
+      <c r="C1499" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="D1499" s="8">
+        <v>4008911</v>
+      </c>
+      <c r="E1499" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1499" s="9">
+        <v>46228</v>
+      </c>
+      <c r="G1499" s="8">
+        <v>51.93</v>
+      </c>
+      <c r="H1499" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1499" s="8">
+        <v>51.93</v>
+      </c>
+      <c r="J1499" s="6">
+        <f t="shared" si="47"/>
+        <v>48.8142</v>
+      </c>
+      <c r="L1499" s="6">
+        <f t="shared" si="46"/>
+        <v>48.8142</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1500" s="8">
+        <v>21</v>
+      </c>
+      <c r="B1500" s="8">
+        <v>9701041854</v>
+      </c>
+      <c r="C1500" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="D1500" s="8">
+        <v>202617806</v>
+      </c>
+      <c r="E1500" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1500" s="9">
+        <v>46230</v>
+      </c>
+      <c r="G1500" s="8">
+        <v>14.77</v>
+      </c>
+      <c r="H1500" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1500" s="8">
+        <v>14.77</v>
+      </c>
+      <c r="J1500" s="6">
+        <f t="shared" si="47"/>
+        <v>13.883799999999999</v>
+      </c>
+      <c r="L1500" s="6">
+        <f t="shared" si="46"/>
+        <v>13.883799999999999</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1501" s="8">
+        <v>22</v>
+      </c>
+      <c r="B1501" s="8">
+        <v>9991062435</v>
+      </c>
+      <c r="C1501" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D1501" s="8">
+        <v>202617884</v>
+      </c>
+      <c r="E1501" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1501" s="9">
+        <v>46231</v>
+      </c>
+      <c r="G1501" s="8">
+        <v>33.770000000000003</v>
+      </c>
+      <c r="H1501" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1501" s="8">
+        <v>33.770000000000003</v>
+      </c>
+      <c r="J1501" s="6">
+        <f t="shared" si="47"/>
+        <v>31.7438</v>
+      </c>
+      <c r="L1501" s="6">
+        <f t="shared" si="46"/>
+        <v>31.7438</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1502" s="8">
+        <v>23</v>
+      </c>
+      <c r="B1502" s="8">
+        <v>9882000587</v>
+      </c>
+      <c r="C1502" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1502" s="8">
+        <v>202617915</v>
+      </c>
+      <c r="E1502" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1502" s="9">
+        <v>46231</v>
+      </c>
+      <c r="G1502" s="8">
+        <v>39.520000000000003</v>
+      </c>
+      <c r="H1502" s="8">
+        <v>0</v>
+      </c>
+      <c r="I1502" s="8">
+        <v>39.520000000000003</v>
+      </c>
+      <c r="J1502" s="6">
+        <f t="shared" si="47"/>
+        <v>37.148800000000001</v>
+      </c>
+      <c r="L1502" s="6">
+        <f t="shared" si="46"/>
+        <v>37.148800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/نات هيلث للتأمين.xlsx
+++ b/نات هيلث للتأمين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEE3765-E67E-4F59-BD6C-BC524A285706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E0A762-6751-4A62-A541-B8C293170510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1DC53A1F-76F9-410D-8A40-2032C97E1510}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="702">
   <si>
     <t>الرقم</t>
   </si>
@@ -2133,6 +2133,15 @@
   </si>
   <si>
     <t>جود رائد الصبيحات</t>
+  </si>
+  <si>
+    <t>عائشة هارون الخلايفة</t>
+  </si>
+  <si>
+    <t>جود اياد المساعدة</t>
+  </si>
+  <si>
+    <t>شام موسى المساعدة</t>
   </si>
 </sst>
 </file>
@@ -2194,7 +2203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2202,9 +2211,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2539,7 +2545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22865DC0-B890-4D8D-83EE-833A3F5E241E}">
-  <dimension ref="A1:L1502"/>
+  <dimension ref="A1:L1529"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -56812,7 +56818,7 @@
       </c>
       <c r="K1466"/>
       <c r="L1466" s="6">
-        <f t="shared" ref="L1466:L1502" si="46">J1466-K1466</f>
+        <f t="shared" ref="L1466:L1528" si="46">J1466-K1466</f>
         <v>25.857199999999995</v>
       </c>
     </row>
@@ -57141,7 +57147,7 @@
         <v>20.824000000000002</v>
       </c>
       <c r="J1475" s="6">
-        <f t="shared" ref="J1475:J1502" si="47">G1475*0.94-H1475</f>
+        <f t="shared" ref="J1475:J1529" si="47">G1475*0.94-H1475</f>
         <v>19.43572</v>
       </c>
       <c r="L1475" s="6">
@@ -57298,487 +57304,487 @@
       </c>
     </row>
     <row r="1480" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1480" s="8">
+      <c r="A1480" s="2">
         <v>1</v>
       </c>
-      <c r="B1480" s="8">
+      <c r="B1480" s="2">
         <v>9592022140</v>
       </c>
-      <c r="C1480" s="8" t="s">
+      <c r="C1480" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1480" s="8">
+      <c r="D1480" s="2">
         <v>596545</v>
       </c>
-      <c r="E1480" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1480" s="9">
+      <c r="E1480" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1480" s="3">
         <v>46205</v>
       </c>
-      <c r="G1480" s="8">
+      <c r="G1480" s="2">
         <v>95.74</v>
       </c>
-      <c r="H1480" s="8">
+      <c r="H1480" s="2">
         <v>23.934999999999999</v>
       </c>
-      <c r="I1480" s="8">
+      <c r="I1480" s="2">
         <v>71.805000000000007</v>
       </c>
       <c r="J1480" s="6">
         <f t="shared" si="47"/>
         <v>66.060599999999994</v>
       </c>
-      <c r="K1480" s="7"/>
+      <c r="K1480"/>
       <c r="L1480" s="6">
         <f t="shared" si="46"/>
         <v>66.060599999999994</v>
       </c>
     </row>
     <row r="1481" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1481" s="8">
+      <c r="A1481" s="2">
         <v>2</v>
       </c>
-      <c r="B1481" s="8">
+      <c r="B1481" s="2">
         <v>9991062435</v>
       </c>
-      <c r="C1481" s="8" t="s">
+      <c r="C1481" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D1481" s="8">
+      <c r="D1481" s="2">
         <v>202615788</v>
       </c>
-      <c r="E1481" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1481" s="9">
+      <c r="E1481" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1481" s="3">
         <v>46207</v>
       </c>
-      <c r="G1481" s="8">
+      <c r="G1481" s="2">
         <v>7.25</v>
       </c>
-      <c r="H1481" s="8">
+      <c r="H1481" s="2">
         <v>0</v>
       </c>
-      <c r="I1481" s="8">
+      <c r="I1481" s="2">
         <v>7.25</v>
       </c>
       <c r="J1481" s="6">
         <f t="shared" si="47"/>
         <v>6.8149999999999995</v>
       </c>
-      <c r="K1481" s="7"/>
+      <c r="K1481"/>
       <c r="L1481" s="6">
         <f t="shared" si="46"/>
         <v>6.8149999999999995</v>
       </c>
     </row>
     <row r="1482" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1482" s="8">
+      <c r="A1482" s="2">
         <v>3</v>
       </c>
-      <c r="B1482" s="8">
+      <c r="B1482" s="2">
         <v>40088621</v>
       </c>
-      <c r="C1482" s="8" t="s">
+      <c r="C1482" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="D1482" s="8">
+      <c r="D1482" s="2">
         <v>202615789</v>
       </c>
-      <c r="E1482" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1482" s="9">
+      <c r="E1482" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1482" s="3">
         <v>46207</v>
       </c>
-      <c r="G1482" s="8">
+      <c r="G1482" s="2">
         <v>13.75</v>
       </c>
-      <c r="H1482" s="8">
+      <c r="H1482" s="2">
         <v>0</v>
       </c>
-      <c r="I1482" s="8">
+      <c r="I1482" s="2">
         <v>13.75</v>
       </c>
       <c r="J1482" s="6">
         <f t="shared" si="47"/>
         <v>12.924999999999999</v>
       </c>
-      <c r="K1482" s="7"/>
+      <c r="K1482"/>
       <c r="L1482" s="6">
         <f t="shared" si="46"/>
         <v>12.924999999999999</v>
       </c>
     </row>
     <row r="1483" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1483" s="8">
+      <c r="A1483" s="2">
         <v>4</v>
       </c>
-      <c r="B1483" s="8">
+      <c r="B1483" s="2">
         <v>9001158701</v>
       </c>
-      <c r="C1483" s="8" t="s">
+      <c r="C1483" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D1483" s="8">
+      <c r="D1483" s="2">
         <v>9001157</v>
       </c>
-      <c r="E1483" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1483" s="9">
+      <c r="E1483" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1483" s="3">
         <v>46211</v>
       </c>
-      <c r="G1483" s="8">
+      <c r="G1483" s="2">
         <v>21.65</v>
       </c>
-      <c r="H1483" s="8">
+      <c r="H1483" s="2">
         <v>6.4950000000000001</v>
       </c>
-      <c r="I1483" s="8">
+      <c r="I1483" s="2">
         <v>15.154999999999999</v>
       </c>
       <c r="J1483" s="6">
         <f t="shared" si="47"/>
         <v>13.855999999999998</v>
       </c>
-      <c r="K1483" s="7"/>
+      <c r="K1483"/>
       <c r="L1483" s="6">
         <f t="shared" si="46"/>
         <v>13.855999999999998</v>
       </c>
     </row>
     <row r="1484" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1484" s="8">
+      <c r="A1484" s="2">
         <v>5</v>
       </c>
-      <c r="B1484" s="8">
+      <c r="B1484" s="2">
         <v>9531015239</v>
       </c>
-      <c r="C1484" s="8" t="s">
+      <c r="C1484" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D1484" s="8">
+      <c r="D1484" s="2">
         <v>202616177</v>
       </c>
-      <c r="E1484" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1484" s="9">
+      <c r="E1484" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1484" s="3">
         <v>46212</v>
       </c>
-      <c r="G1484" s="8">
+      <c r="G1484" s="2">
         <v>86.58</v>
       </c>
-      <c r="H1484" s="8">
+      <c r="H1484" s="2">
         <v>12.987</v>
       </c>
-      <c r="I1484" s="8">
+      <c r="I1484" s="2">
         <v>73.593000000000004</v>
       </c>
       <c r="J1484" s="6">
         <f t="shared" si="47"/>
         <v>68.398200000000003</v>
       </c>
-      <c r="K1484" s="7"/>
+      <c r="K1484"/>
       <c r="L1484" s="6">
         <f t="shared" si="46"/>
         <v>68.398200000000003</v>
       </c>
     </row>
     <row r="1485" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1485" s="8">
+      <c r="A1485" s="2">
         <v>6</v>
       </c>
-      <c r="B1485" s="8">
+      <c r="B1485" s="2">
         <v>2004143124</v>
       </c>
-      <c r="C1485" s="8" t="s">
+      <c r="C1485" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D1485" s="8">
+      <c r="D1485" s="2">
         <v>202616385</v>
       </c>
-      <c r="E1485" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1485" s="9">
+      <c r="E1485" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1485" s="3">
         <v>46214</v>
       </c>
-      <c r="G1485" s="8">
+      <c r="G1485" s="2">
         <v>23.75</v>
       </c>
-      <c r="H1485" s="8">
+      <c r="H1485" s="2">
         <v>3.5619999999999998</v>
       </c>
-      <c r="I1485" s="8">
+      <c r="I1485" s="2">
         <v>20.187999999999999</v>
       </c>
       <c r="J1485" s="6">
         <f t="shared" si="47"/>
         <v>18.762999999999998</v>
       </c>
-      <c r="K1485" s="7"/>
+      <c r="K1485"/>
       <c r="L1485" s="6">
         <f t="shared" si="46"/>
         <v>18.762999999999998</v>
       </c>
     </row>
     <row r="1486" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1486" s="8">
+      <c r="A1486" s="2">
         <v>7</v>
       </c>
-      <c r="B1486" s="8">
+      <c r="B1486" s="2">
         <v>9861028995</v>
       </c>
-      <c r="C1486" s="8" t="s">
+      <c r="C1486" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D1486" s="8">
+      <c r="D1486" s="2">
         <v>202616386</v>
       </c>
-      <c r="E1486" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1486" s="9">
+      <c r="E1486" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1486" s="3">
         <v>46214</v>
       </c>
-      <c r="G1486" s="8">
+      <c r="G1486" s="2">
         <v>19.72</v>
       </c>
-      <c r="H1486" s="8">
+      <c r="H1486" s="2">
         <v>2.9580000000000002</v>
       </c>
-      <c r="I1486" s="8">
+      <c r="I1486" s="2">
         <v>16.762</v>
       </c>
       <c r="J1486" s="6">
         <f t="shared" si="47"/>
         <v>15.578799999999999</v>
       </c>
-      <c r="K1486" s="7"/>
+      <c r="K1486"/>
       <c r="L1486" s="6">
         <f t="shared" si="46"/>
         <v>15.578799999999999</v>
       </c>
     </row>
     <row r="1487" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1487" s="8">
+      <c r="A1487" s="2">
         <v>8</v>
       </c>
-      <c r="B1487" s="8">
+      <c r="B1487" s="2">
         <v>2003171719</v>
       </c>
-      <c r="C1487" s="8" t="s">
+      <c r="C1487" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="D1487" s="8">
+      <c r="D1487" s="2">
         <v>202616387</v>
       </c>
-      <c r="E1487" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1487" s="9">
+      <c r="E1487" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1487" s="3">
         <v>46214</v>
       </c>
-      <c r="G1487" s="8">
+      <c r="G1487" s="2">
         <v>13.51</v>
       </c>
-      <c r="H1487" s="8">
+      <c r="H1487" s="2">
         <v>2.0259999999999998</v>
       </c>
-      <c r="I1487" s="8">
+      <c r="I1487" s="2">
         <v>11.484</v>
       </c>
       <c r="J1487" s="6">
         <f t="shared" si="47"/>
         <v>10.673399999999999</v>
       </c>
-      <c r="K1487" s="7"/>
+      <c r="K1487"/>
       <c r="L1487" s="6">
         <f t="shared" si="46"/>
         <v>10.673399999999999</v>
       </c>
     </row>
     <row r="1488" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1488" s="8">
-        <v>9</v>
-      </c>
-      <c r="B1488" s="8">
+      <c r="A1488" s="2">
+        <v>9</v>
+      </c>
+      <c r="B1488" s="2">
         <v>200439018</v>
       </c>
-      <c r="C1488" s="8" t="s">
+      <c r="C1488" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D1488" s="8">
+      <c r="D1488" s="2">
         <v>202616388</v>
       </c>
-      <c r="E1488" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1488" s="9">
+      <c r="E1488" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1488" s="3">
         <v>46214</v>
       </c>
-      <c r="G1488" s="8">
+      <c r="G1488" s="2">
         <v>48.07</v>
       </c>
-      <c r="H1488" s="8">
+      <c r="H1488" s="2">
         <v>7.21</v>
       </c>
-      <c r="I1488" s="8">
+      <c r="I1488" s="2">
         <v>40.86</v>
       </c>
       <c r="J1488" s="6">
         <f t="shared" si="47"/>
         <v>37.9758</v>
       </c>
-      <c r="K1488" s="7"/>
+      <c r="K1488"/>
       <c r="L1488" s="6">
         <f t="shared" si="46"/>
         <v>37.9758</v>
       </c>
     </row>
     <row r="1489" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1489" s="8">
+      <c r="A1489" s="2">
         <v>10</v>
       </c>
-      <c r="B1489" s="8">
+      <c r="B1489" s="2">
         <v>9662041156</v>
       </c>
-      <c r="C1489" s="8" t="s">
+      <c r="C1489" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D1489" s="8">
+      <c r="D1489" s="2">
         <v>96620414</v>
       </c>
-      <c r="E1489" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1489" s="9">
+      <c r="E1489" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1489" s="3">
         <v>46214</v>
       </c>
-      <c r="G1489" s="8">
+      <c r="G1489" s="2">
         <v>56.21</v>
       </c>
-      <c r="H1489" s="8">
+      <c r="H1489" s="2">
         <v>11.242000000000001</v>
       </c>
-      <c r="I1489" s="8">
+      <c r="I1489" s="2">
         <v>44.968000000000004</v>
       </c>
       <c r="J1489" s="6">
         <f t="shared" si="47"/>
         <v>41.595399999999998</v>
       </c>
-      <c r="K1489" s="7"/>
+      <c r="K1489"/>
       <c r="L1489" s="6">
         <f t="shared" si="46"/>
         <v>41.595399999999998</v>
       </c>
     </row>
     <row r="1490" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1490" s="8">
-        <v>11</v>
-      </c>
-      <c r="B1490" s="8">
+      <c r="A1490" s="2">
+        <v>11</v>
+      </c>
+      <c r="B1490" s="2">
         <v>40220569</v>
       </c>
-      <c r="C1490" s="8" t="s">
+      <c r="C1490" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D1490" s="8">
+      <c r="D1490" s="2">
         <v>202616500</v>
       </c>
-      <c r="E1490" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1490" s="9">
+      <c r="E1490" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1490" s="3">
         <v>46215</v>
       </c>
-      <c r="G1490" s="8">
+      <c r="G1490" s="2">
         <v>34.700000000000003</v>
       </c>
-      <c r="H1490" s="8">
+      <c r="H1490" s="2">
         <v>3.47</v>
       </c>
-      <c r="I1490" s="8">
+      <c r="I1490" s="2">
         <v>31.23</v>
       </c>
       <c r="J1490" s="6">
         <f t="shared" si="47"/>
         <v>29.148000000000003</v>
       </c>
-      <c r="K1490" s="7"/>
+      <c r="K1490"/>
       <c r="L1490" s="6">
         <f t="shared" si="46"/>
         <v>29.148000000000003</v>
       </c>
     </row>
     <row r="1491" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1491" s="8">
+      <c r="A1491" s="2">
         <v>12</v>
       </c>
-      <c r="B1491" s="8">
+      <c r="B1491" s="2">
         <v>40087410</v>
       </c>
-      <c r="C1491" s="8" t="s">
+      <c r="C1491" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D1491" s="8">
+      <c r="D1491" s="2">
         <v>4008411</v>
       </c>
-      <c r="E1491" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1491" s="9">
+      <c r="E1491" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1491" s="3">
         <v>46218</v>
       </c>
-      <c r="G1491" s="8">
+      <c r="G1491" s="2">
         <v>53.9</v>
       </c>
-      <c r="H1491" s="8">
+      <c r="H1491" s="2">
         <v>0</v>
       </c>
-      <c r="I1491" s="8">
+      <c r="I1491" s="2">
         <v>53.9</v>
       </c>
       <c r="J1491" s="6">
         <f t="shared" si="47"/>
         <v>50.665999999999997</v>
       </c>
-      <c r="K1491" s="7"/>
+      <c r="K1491"/>
       <c r="L1491" s="6">
         <f t="shared" si="46"/>
         <v>50.665999999999997</v>
       </c>
     </row>
     <row r="1492" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1492" s="8">
+      <c r="A1492" s="2">
         <v>13</v>
       </c>
-      <c r="B1492" s="8">
+      <c r="B1492" s="2">
         <v>9572020006</v>
       </c>
-      <c r="C1492" s="8" t="s">
+      <c r="C1492" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D1492" s="8">
+      <c r="D1492" s="2">
         <v>9572021212</v>
       </c>
-      <c r="E1492" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1492" s="9">
+      <c r="E1492" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1492" s="3">
         <v>46219</v>
       </c>
-      <c r="G1492" s="8">
+      <c r="G1492" s="2">
         <v>71.400000000000006</v>
       </c>
-      <c r="H1492" s="8">
+      <c r="H1492" s="2">
         <v>17.850000000000001</v>
       </c>
-      <c r="I1492" s="8">
+      <c r="I1492" s="2">
         <v>53.55</v>
       </c>
       <c r="J1492" s="6">
@@ -57791,31 +57797,31 @@
       </c>
     </row>
     <row r="1493" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1493" s="8">
+      <c r="A1493" s="2">
         <v>14</v>
       </c>
-      <c r="B1493" s="8">
+      <c r="B1493" s="2">
         <v>9851047616</v>
       </c>
-      <c r="C1493" s="8" t="s">
+      <c r="C1493" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D1493" s="8">
+      <c r="D1493" s="2">
         <v>202616916</v>
       </c>
-      <c r="E1493" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1493" s="9">
+      <c r="E1493" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1493" s="3">
         <v>46221</v>
       </c>
-      <c r="G1493" s="8">
+      <c r="G1493" s="2">
         <v>52.84</v>
       </c>
-      <c r="H1493" s="8">
+      <c r="H1493" s="2">
         <v>0</v>
       </c>
-      <c r="I1493" s="8">
+      <c r="I1493" s="2">
         <v>52.84</v>
       </c>
       <c r="J1493" s="6">
@@ -57828,31 +57834,31 @@
       </c>
     </row>
     <row r="1494" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1494" s="8">
+      <c r="A1494" s="2">
         <v>15</v>
       </c>
-      <c r="B1494" s="8">
+      <c r="B1494" s="2">
         <v>2004423187</v>
       </c>
-      <c r="C1494" s="8" t="s">
+      <c r="C1494" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="D1494" s="8">
+      <c r="D1494" s="2">
         <v>202616917</v>
       </c>
-      <c r="E1494" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1494" s="9">
+      <c r="E1494" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1494" s="3">
         <v>46221</v>
       </c>
-      <c r="G1494" s="8">
+      <c r="G1494" s="2">
         <v>24.46</v>
       </c>
-      <c r="H1494" s="8">
+      <c r="H1494" s="2">
         <v>0</v>
       </c>
-      <c r="I1494" s="8">
+      <c r="I1494" s="2">
         <v>24.46</v>
       </c>
       <c r="J1494" s="6">
@@ -57865,31 +57871,31 @@
       </c>
     </row>
     <row r="1495" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1495" s="8">
+      <c r="A1495" s="2">
         <v>16</v>
       </c>
-      <c r="B1495" s="8">
+      <c r="B1495" s="2">
         <v>9552017225</v>
       </c>
-      <c r="C1495" s="8" t="s">
+      <c r="C1495" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D1495" s="8">
+      <c r="D1495" s="2">
         <v>17225</v>
       </c>
-      <c r="E1495" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1495" s="9">
+      <c r="E1495" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1495" s="3">
         <v>46223</v>
       </c>
-      <c r="G1495" s="8">
+      <c r="G1495" s="2">
         <v>25.11</v>
       </c>
-      <c r="H1495" s="8">
+      <c r="H1495" s="2">
         <v>3.766</v>
       </c>
-      <c r="I1495" s="8">
+      <c r="I1495" s="2">
         <v>21.344000000000001</v>
       </c>
       <c r="J1495" s="6">
@@ -57902,31 +57908,31 @@
       </c>
     </row>
     <row r="1496" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1496" s="8">
+      <c r="A1496" s="2">
         <v>17</v>
       </c>
-      <c r="B1496" s="8">
+      <c r="B1496" s="2">
         <v>9771047773</v>
       </c>
-      <c r="C1496" s="8" t="s">
+      <c r="C1496" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D1496" s="8">
+      <c r="D1496" s="2">
         <v>1047773</v>
       </c>
-      <c r="E1496" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1496" s="9">
+      <c r="E1496" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1496" s="3">
         <v>46223</v>
       </c>
-      <c r="G1496" s="8">
+      <c r="G1496" s="2">
         <v>38.31</v>
       </c>
-      <c r="H1496" s="8">
+      <c r="H1496" s="2">
         <v>7.6619999999999999</v>
       </c>
-      <c r="I1496" s="8">
+      <c r="I1496" s="2">
         <v>30.648</v>
       </c>
       <c r="J1496" s="6">
@@ -57939,31 +57945,31 @@
       </c>
     </row>
     <row r="1497" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1497" s="8">
+      <c r="A1497" s="2">
         <v>18</v>
       </c>
-      <c r="B1497" s="8">
+      <c r="B1497" s="2">
         <v>9602026931</v>
       </c>
-      <c r="C1497" s="8" t="s">
+      <c r="C1497" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="D1497" s="8">
+      <c r="D1497" s="2">
         <v>202617181</v>
       </c>
-      <c r="E1497" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1497" s="9">
+      <c r="E1497" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1497" s="3">
         <v>46224</v>
       </c>
-      <c r="G1497" s="8">
+      <c r="G1497" s="2">
         <v>71.239999999999995</v>
       </c>
-      <c r="H1497" s="8">
+      <c r="H1497" s="2">
         <v>10.686</v>
       </c>
-      <c r="I1497" s="8">
+      <c r="I1497" s="2">
         <v>60.554000000000002</v>
       </c>
       <c r="J1497" s="6">
@@ -57976,31 +57982,31 @@
       </c>
     </row>
     <row r="1498" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1498" s="8">
+      <c r="A1498" s="2">
         <v>19</v>
       </c>
-      <c r="B1498" s="8">
+      <c r="B1498" s="2">
         <v>40089015</v>
       </c>
-      <c r="C1498" s="8" t="s">
+      <c r="C1498" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D1498" s="8">
+      <c r="D1498" s="2">
         <v>4008945</v>
       </c>
-      <c r="E1498" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1498" s="9">
+      <c r="E1498" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1498" s="3">
         <v>46228</v>
       </c>
-      <c r="G1498" s="8">
+      <c r="G1498" s="2">
         <v>46.17</v>
       </c>
-      <c r="H1498" s="8">
+      <c r="H1498" s="2">
         <v>0</v>
       </c>
-      <c r="I1498" s="8">
+      <c r="I1498" s="2">
         <v>46.17</v>
       </c>
       <c r="J1498" s="6">
@@ -58013,31 +58019,31 @@
       </c>
     </row>
     <row r="1499" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1499" s="8">
+      <c r="A1499" s="2">
         <v>20</v>
       </c>
-      <c r="B1499" s="8">
+      <c r="B1499" s="2">
         <v>40089016</v>
       </c>
-      <c r="C1499" s="8" t="s">
+      <c r="C1499" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="D1499" s="8">
+      <c r="D1499" s="2">
         <v>4008911</v>
       </c>
-      <c r="E1499" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1499" s="9">
+      <c r="E1499" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1499" s="3">
         <v>46228</v>
       </c>
-      <c r="G1499" s="8">
+      <c r="G1499" s="2">
         <v>51.93</v>
       </c>
-      <c r="H1499" s="8">
+      <c r="H1499" s="2">
         <v>0</v>
       </c>
-      <c r="I1499" s="8">
+      <c r="I1499" s="2">
         <v>51.93</v>
       </c>
       <c r="J1499" s="6">
@@ -58050,31 +58056,31 @@
       </c>
     </row>
     <row r="1500" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1500" s="8">
+      <c r="A1500" s="2">
         <v>21</v>
       </c>
-      <c r="B1500" s="8">
+      <c r="B1500" s="2">
         <v>9701041854</v>
       </c>
-      <c r="C1500" s="8" t="s">
+      <c r="C1500" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D1500" s="8">
+      <c r="D1500" s="2">
         <v>202617806</v>
       </c>
-      <c r="E1500" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1500" s="9">
+      <c r="E1500" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1500" s="3">
         <v>46230</v>
       </c>
-      <c r="G1500" s="8">
+      <c r="G1500" s="2">
         <v>14.77</v>
       </c>
-      <c r="H1500" s="8">
+      <c r="H1500" s="2">
         <v>0</v>
       </c>
-      <c r="I1500" s="8">
+      <c r="I1500" s="2">
         <v>14.77</v>
       </c>
       <c r="J1500" s="6">
@@ -58087,31 +58093,31 @@
       </c>
     </row>
     <row r="1501" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1501" s="8">
+      <c r="A1501" s="2">
         <v>22</v>
       </c>
-      <c r="B1501" s="8">
+      <c r="B1501" s="2">
         <v>9991062435</v>
       </c>
-      <c r="C1501" s="8" t="s">
+      <c r="C1501" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D1501" s="8">
+      <c r="D1501" s="2">
         <v>202617884</v>
       </c>
-      <c r="E1501" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1501" s="9">
+      <c r="E1501" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1501" s="3">
         <v>46231</v>
       </c>
-      <c r="G1501" s="8">
+      <c r="G1501" s="2">
         <v>33.770000000000003</v>
       </c>
-      <c r="H1501" s="8">
+      <c r="H1501" s="2">
         <v>0</v>
       </c>
-      <c r="I1501" s="8">
+      <c r="I1501" s="2">
         <v>33.770000000000003</v>
       </c>
       <c r="J1501" s="6">
@@ -58124,31 +58130,31 @@
       </c>
     </row>
     <row r="1502" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1502" s="8">
+      <c r="A1502" s="2">
         <v>23</v>
       </c>
-      <c r="B1502" s="8">
+      <c r="B1502" s="2">
         <v>9882000587</v>
       </c>
-      <c r="C1502" s="8" t="s">
+      <c r="C1502" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D1502" s="8">
+      <c r="D1502" s="2">
         <v>202617915</v>
       </c>
-      <c r="E1502" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1502" s="9">
+      <c r="E1502" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1502" s="3">
         <v>46231</v>
       </c>
-      <c r="G1502" s="8">
+      <c r="G1502" s="2">
         <v>39.520000000000003</v>
       </c>
-      <c r="H1502" s="8">
+      <c r="H1502" s="2">
         <v>0</v>
       </c>
-      <c r="I1502" s="8">
+      <c r="I1502" s="2">
         <v>39.520000000000003</v>
       </c>
       <c r="J1502" s="6">
@@ -58158,6 +58164,1032 @@
       <c r="L1502" s="6">
         <f t="shared" si="46"/>
         <v>37.148800000000001</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1503" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1503" s="2">
+        <v>2004960798</v>
+      </c>
+      <c r="C1503" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D1503" s="2">
+        <v>20049656</v>
+      </c>
+      <c r="E1503" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1503" s="3">
+        <v>46235</v>
+      </c>
+      <c r="G1503" s="2">
+        <v>20.59</v>
+      </c>
+      <c r="H1503" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1503" s="2">
+        <v>20.59</v>
+      </c>
+      <c r="J1503" s="6">
+        <f t="shared" si="47"/>
+        <v>19.354599999999998</v>
+      </c>
+      <c r="K1503"/>
+      <c r="L1503" s="6">
+        <f t="shared" si="46"/>
+        <v>19.354599999999998</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1504" s="2">
+        <v>2</v>
+      </c>
+      <c r="B1504" s="2">
+        <v>2004404730</v>
+      </c>
+      <c r="C1504" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D1504" s="2">
+        <v>2004415</v>
+      </c>
+      <c r="E1504" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1504" s="3">
+        <v>46235</v>
+      </c>
+      <c r="G1504" s="2">
+        <v>35.979999999999997</v>
+      </c>
+      <c r="H1504" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1504" s="2">
+        <v>35.979999999999997</v>
+      </c>
+      <c r="J1504" s="6">
+        <f t="shared" si="47"/>
+        <v>33.821199999999997</v>
+      </c>
+      <c r="K1504"/>
+      <c r="L1504" s="6">
+        <f t="shared" si="46"/>
+        <v>33.821199999999997</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1505" s="2">
+        <v>3</v>
+      </c>
+      <c r="B1505" s="2">
+        <v>2003171719</v>
+      </c>
+      <c r="C1505" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D1505" s="2">
+        <v>20031414</v>
+      </c>
+      <c r="E1505" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1505" s="3">
+        <v>46235</v>
+      </c>
+      <c r="G1505" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="H1505" s="2">
+        <v>2.2949999999999999</v>
+      </c>
+      <c r="I1505" s="2">
+        <v>13.005000000000001</v>
+      </c>
+      <c r="J1505" s="6">
+        <f t="shared" si="47"/>
+        <v>12.087</v>
+      </c>
+      <c r="K1505"/>
+      <c r="L1505" s="6">
+        <f t="shared" si="46"/>
+        <v>12.087</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1506" s="2">
+        <v>4</v>
+      </c>
+      <c r="B1506" s="2">
+        <v>9912055798</v>
+      </c>
+      <c r="C1506" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D1506" s="2">
+        <v>99120411</v>
+      </c>
+      <c r="E1506" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1506" s="3">
+        <v>46235</v>
+      </c>
+      <c r="G1506" s="2">
+        <v>22.71</v>
+      </c>
+      <c r="H1506" s="2">
+        <v>3.4060000000000001</v>
+      </c>
+      <c r="I1506" s="2">
+        <v>19.303999999999998</v>
+      </c>
+      <c r="J1506" s="6">
+        <f t="shared" si="47"/>
+        <v>17.941400000000002</v>
+      </c>
+      <c r="K1506"/>
+      <c r="L1506" s="6">
+        <f t="shared" si="46"/>
+        <v>17.941400000000002</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1507" s="2">
+        <v>5</v>
+      </c>
+      <c r="B1507" s="2">
+        <v>2004143124</v>
+      </c>
+      <c r="C1507" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D1507" s="2">
+        <v>2001412</v>
+      </c>
+      <c r="E1507" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1507" s="3">
+        <v>46235</v>
+      </c>
+      <c r="G1507" s="2">
+        <v>10.79</v>
+      </c>
+      <c r="H1507" s="2">
+        <v>1.6180000000000001</v>
+      </c>
+      <c r="I1507" s="2">
+        <v>9.1720000000000006</v>
+      </c>
+      <c r="J1507" s="6">
+        <f t="shared" si="47"/>
+        <v>8.5245999999999977</v>
+      </c>
+      <c r="K1507"/>
+      <c r="L1507" s="6">
+        <f t="shared" si="46"/>
+        <v>8.5245999999999977</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1508" s="2">
+        <v>6</v>
+      </c>
+      <c r="B1508" s="2">
+        <v>9592022140</v>
+      </c>
+      <c r="C1508" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1508" s="2">
+        <v>2022140</v>
+      </c>
+      <c r="E1508" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1508" s="3">
+        <v>46235</v>
+      </c>
+      <c r="G1508" s="2">
+        <v>88.93</v>
+      </c>
+      <c r="H1508" s="2">
+        <v>22.231999999999999</v>
+      </c>
+      <c r="I1508" s="2">
+        <v>66.697999999999993</v>
+      </c>
+      <c r="J1508" s="6">
+        <f t="shared" si="47"/>
+        <v>61.362200000000001</v>
+      </c>
+      <c r="K1508"/>
+      <c r="L1508" s="6">
+        <f t="shared" si="46"/>
+        <v>61.362200000000001</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1509" s="2">
+        <v>7</v>
+      </c>
+      <c r="B1509" s="2">
+        <v>9771047773</v>
+      </c>
+      <c r="C1509" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1509" s="2">
+        <v>97710412</v>
+      </c>
+      <c r="E1509" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1509" s="3">
+        <v>46239</v>
+      </c>
+      <c r="G1509" s="2">
+        <v>58.48</v>
+      </c>
+      <c r="H1509" s="2">
+        <v>11.696</v>
+      </c>
+      <c r="I1509" s="2">
+        <v>46.783999999999999</v>
+      </c>
+      <c r="J1509" s="6">
+        <f t="shared" si="47"/>
+        <v>43.275199999999998</v>
+      </c>
+      <c r="K1509"/>
+      <c r="L1509" s="6">
+        <f t="shared" si="46"/>
+        <v>43.275199999999998</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1510" s="2">
+        <v>8</v>
+      </c>
+      <c r="B1510" s="2">
+        <v>9602026931</v>
+      </c>
+      <c r="C1510" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1510" s="2">
+        <v>202618592</v>
+      </c>
+      <c r="E1510" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1510" s="3">
+        <v>46240</v>
+      </c>
+      <c r="G1510" s="2">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="H1510" s="2">
+        <v>2.7759999999999998</v>
+      </c>
+      <c r="I1510" s="2">
+        <v>15.734</v>
+      </c>
+      <c r="J1510" s="6">
+        <f t="shared" si="47"/>
+        <v>14.6234</v>
+      </c>
+      <c r="K1510"/>
+      <c r="L1510" s="6">
+        <f t="shared" si="46"/>
+        <v>14.6234</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1511" s="2">
+        <v>9</v>
+      </c>
+      <c r="B1511" s="2">
+        <v>9531015239</v>
+      </c>
+      <c r="C1511" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1511" s="2">
+        <v>202618931</v>
+      </c>
+      <c r="E1511" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1511" s="3">
+        <v>46244</v>
+      </c>
+      <c r="G1511" s="2">
+        <v>86.58</v>
+      </c>
+      <c r="H1511" s="2">
+        <v>12.987</v>
+      </c>
+      <c r="I1511" s="2">
+        <v>73.593000000000004</v>
+      </c>
+      <c r="J1511" s="6">
+        <f t="shared" si="47"/>
+        <v>68.398200000000003</v>
+      </c>
+      <c r="K1511"/>
+      <c r="L1511" s="6">
+        <f t="shared" si="46"/>
+        <v>68.398200000000003</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1512" s="2">
+        <v>10</v>
+      </c>
+      <c r="B1512" s="2">
+        <v>40220569</v>
+      </c>
+      <c r="C1512" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1512" s="2">
+        <v>202618999</v>
+      </c>
+      <c r="E1512" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1512" s="3">
+        <v>46245</v>
+      </c>
+      <c r="G1512" s="2">
+        <v>31.77</v>
+      </c>
+      <c r="H1512" s="2">
+        <v>3.177</v>
+      </c>
+      <c r="I1512" s="2">
+        <v>28.593</v>
+      </c>
+      <c r="J1512" s="6">
+        <f t="shared" si="47"/>
+        <v>26.686799999999998</v>
+      </c>
+      <c r="K1512"/>
+      <c r="L1512" s="6">
+        <f t="shared" si="46"/>
+        <v>26.686799999999998</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1513" s="2">
+        <v>11</v>
+      </c>
+      <c r="B1513" s="2">
+        <v>40220568</v>
+      </c>
+      <c r="C1513" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D1513" s="2">
+        <v>202619005</v>
+      </c>
+      <c r="E1513" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1513" s="3">
+        <v>46245</v>
+      </c>
+      <c r="G1513" s="2">
+        <v>39.520000000000003</v>
+      </c>
+      <c r="H1513" s="2">
+        <v>3.952</v>
+      </c>
+      <c r="I1513" s="2">
+        <v>35.567999999999998</v>
+      </c>
+      <c r="J1513" s="6">
+        <f t="shared" si="47"/>
+        <v>33.196800000000003</v>
+      </c>
+      <c r="K1513"/>
+      <c r="L1513" s="6">
+        <f t="shared" si="46"/>
+        <v>33.196800000000003</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1514" s="2">
+        <v>12</v>
+      </c>
+      <c r="B1514" s="2">
+        <v>9981042468</v>
+      </c>
+      <c r="C1514" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1514" s="2">
+        <v>202619096</v>
+      </c>
+      <c r="E1514" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1514" s="3">
+        <v>46246</v>
+      </c>
+      <c r="G1514" s="2">
+        <v>46.51</v>
+      </c>
+      <c r="H1514" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1514" s="2">
+        <v>46.51</v>
+      </c>
+      <c r="J1514" s="6">
+        <f t="shared" si="47"/>
+        <v>43.719399999999993</v>
+      </c>
+      <c r="K1514"/>
+      <c r="L1514" s="6">
+        <f t="shared" si="46"/>
+        <v>43.719399999999993</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1515" s="2">
+        <v>13</v>
+      </c>
+      <c r="B1515" s="2">
+        <v>9572020006</v>
+      </c>
+      <c r="C1515" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1515" s="2">
+        <v>95755454</v>
+      </c>
+      <c r="E1515" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1515" s="3">
+        <v>46249</v>
+      </c>
+      <c r="G1515" s="2">
+        <v>71.73</v>
+      </c>
+      <c r="H1515" s="2">
+        <v>17.931999999999999</v>
+      </c>
+      <c r="I1515" s="2">
+        <v>53.798000000000002</v>
+      </c>
+      <c r="J1515" s="6">
+        <f t="shared" si="47"/>
+        <v>49.494199999999992</v>
+      </c>
+      <c r="K1515"/>
+      <c r="L1515" s="6">
+        <f t="shared" si="46"/>
+        <v>49.494199999999992</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1516" s="2">
+        <v>14</v>
+      </c>
+      <c r="B1516" s="2">
+        <v>9911059464</v>
+      </c>
+      <c r="C1516" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D1516" s="2">
+        <v>202619319</v>
+      </c>
+      <c r="E1516" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1516" s="3">
+        <v>46250</v>
+      </c>
+      <c r="G1516" s="2">
+        <v>33.369999999999997</v>
+      </c>
+      <c r="H1516" s="2">
+        <v>8.3420000000000005</v>
+      </c>
+      <c r="I1516" s="2">
+        <v>25.027999999999999</v>
+      </c>
+      <c r="J1516" s="6">
+        <f t="shared" si="47"/>
+        <v>23.025799999999997</v>
+      </c>
+      <c r="K1516"/>
+      <c r="L1516" s="6">
+        <f t="shared" si="46"/>
+        <v>23.025799999999997</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1517" s="2">
+        <v>15</v>
+      </c>
+      <c r="B1517" s="2">
+        <v>40090035</v>
+      </c>
+      <c r="C1517" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D1517" s="2">
+        <v>202619320</v>
+      </c>
+      <c r="E1517" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1517" s="3">
+        <v>46250</v>
+      </c>
+      <c r="G1517" s="2">
+        <v>44.01</v>
+      </c>
+      <c r="H1517" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1517" s="2">
+        <v>44.01</v>
+      </c>
+      <c r="J1517" s="6">
+        <f t="shared" si="47"/>
+        <v>41.369399999999999</v>
+      </c>
+      <c r="K1517"/>
+      <c r="L1517" s="6">
+        <f t="shared" si="46"/>
+        <v>41.369399999999999</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1518" s="2">
+        <v>17</v>
+      </c>
+      <c r="B1518" s="2">
+        <v>40135221</v>
+      </c>
+      <c r="C1518" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D1518" s="2">
+        <v>4013522</v>
+      </c>
+      <c r="E1518" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1518" s="3">
+        <v>46251</v>
+      </c>
+      <c r="G1518" s="2">
+        <v>18.72</v>
+      </c>
+      <c r="H1518" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1518" s="2">
+        <v>18.72</v>
+      </c>
+      <c r="J1518" s="6">
+        <f t="shared" si="47"/>
+        <v>17.596799999999998</v>
+      </c>
+      <c r="K1518"/>
+      <c r="L1518" s="6">
+        <f t="shared" si="46"/>
+        <v>17.596799999999998</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1519" s="2">
+        <v>18</v>
+      </c>
+      <c r="B1519" s="2">
+        <v>9991062435</v>
+      </c>
+      <c r="C1519" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1519" s="2">
+        <v>999102656</v>
+      </c>
+      <c r="E1519" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1519" s="3">
+        <v>46251</v>
+      </c>
+      <c r="G1519" s="2">
+        <v>36.58</v>
+      </c>
+      <c r="H1519" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1519" s="2">
+        <v>36.58</v>
+      </c>
+      <c r="J1519" s="6">
+        <f t="shared" si="47"/>
+        <v>34.385199999999998</v>
+      </c>
+      <c r="K1519"/>
+      <c r="L1519" s="6">
+        <f t="shared" si="46"/>
+        <v>34.385199999999998</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1520" s="2">
+        <v>19</v>
+      </c>
+      <c r="B1520" s="2">
+        <v>2001483736</v>
+      </c>
+      <c r="C1520" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D1520" s="2">
+        <v>202619535</v>
+      </c>
+      <c r="E1520" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1520" s="3">
+        <v>46253</v>
+      </c>
+      <c r="G1520" s="2">
+        <v>30.99</v>
+      </c>
+      <c r="H1520" s="2">
+        <v>3.0990000000000002</v>
+      </c>
+      <c r="I1520" s="2">
+        <v>27.890999999999998</v>
+      </c>
+      <c r="J1520" s="6">
+        <f t="shared" si="47"/>
+        <v>26.031599999999997</v>
+      </c>
+      <c r="K1520"/>
+      <c r="L1520" s="6">
+        <f t="shared" si="46"/>
+        <v>26.031599999999997</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1521" s="2">
+        <v>20</v>
+      </c>
+      <c r="B1521" s="2">
+        <v>2000964572</v>
+      </c>
+      <c r="C1521" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1521" s="2">
+        <v>202619536</v>
+      </c>
+      <c r="E1521" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1521" s="3">
+        <v>46253</v>
+      </c>
+      <c r="G1521" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1521" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="I1521" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="J1521" s="6">
+        <f t="shared" si="47"/>
+        <v>20.16</v>
+      </c>
+      <c r="K1521"/>
+      <c r="L1521" s="6">
+        <f t="shared" si="46"/>
+        <v>20.16</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1522" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1522" s="2">
+        <v>9732046944</v>
+      </c>
+      <c r="C1522" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D1522" s="2">
+        <v>202619604</v>
+      </c>
+      <c r="E1522" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1522" s="3">
+        <v>46254</v>
+      </c>
+      <c r="G1522" s="2">
+        <v>65.58</v>
+      </c>
+      <c r="H1522" s="2">
+        <v>9.8369999999999997</v>
+      </c>
+      <c r="I1522" s="2">
+        <v>55.743000000000002</v>
+      </c>
+      <c r="J1522" s="6">
+        <f t="shared" si="47"/>
+        <v>51.808199999999999</v>
+      </c>
+      <c r="K1522"/>
+      <c r="L1522" s="6">
+        <f t="shared" si="46"/>
+        <v>51.808199999999999</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1523" s="2">
+        <v>22</v>
+      </c>
+      <c r="B1523" s="2">
+        <v>9931061185</v>
+      </c>
+      <c r="C1523" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D1523" s="2">
+        <v>202619611</v>
+      </c>
+      <c r="E1523" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1523" s="3">
+        <v>46254</v>
+      </c>
+      <c r="G1523" s="2">
+        <v>39.380000000000003</v>
+      </c>
+      <c r="H1523" s="2">
+        <v>5.907</v>
+      </c>
+      <c r="I1523" s="2">
+        <v>33.472999999999999</v>
+      </c>
+      <c r="J1523" s="6">
+        <f t="shared" si="47"/>
+        <v>31.110200000000003</v>
+      </c>
+      <c r="K1523"/>
+      <c r="L1523" s="6">
+        <f t="shared" si="46"/>
+        <v>31.110200000000003</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1524" s="2">
+        <v>23</v>
+      </c>
+      <c r="B1524" s="2">
+        <v>9972064548</v>
+      </c>
+      <c r="C1524" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D1524" s="2">
+        <v>9972064548</v>
+      </c>
+      <c r="E1524" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1524" s="3">
+        <v>46254</v>
+      </c>
+      <c r="G1524" s="2">
+        <v>15.87</v>
+      </c>
+      <c r="H1524" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1524" s="2">
+        <v>15.87</v>
+      </c>
+      <c r="J1524" s="6">
+        <f t="shared" si="47"/>
+        <v>14.917799999999998</v>
+      </c>
+      <c r="K1524"/>
+      <c r="L1524" s="6">
+        <f t="shared" si="46"/>
+        <v>14.917799999999998</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1525" s="2">
+        <v>24</v>
+      </c>
+      <c r="B1525" s="2">
+        <v>9552017225</v>
+      </c>
+      <c r="C1525" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1525" s="2">
+        <v>202620124</v>
+      </c>
+      <c r="E1525" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1525" s="3">
+        <v>46259</v>
+      </c>
+      <c r="G1525" s="2">
+        <v>25.23</v>
+      </c>
+      <c r="H1525" s="2">
+        <v>3.7839999999999998</v>
+      </c>
+      <c r="I1525" s="2">
+        <v>21.446000000000002</v>
+      </c>
+      <c r="J1525" s="6">
+        <f t="shared" si="47"/>
+        <v>19.932200000000002</v>
+      </c>
+      <c r="K1525"/>
+      <c r="L1525" s="6">
+        <f t="shared" si="46"/>
+        <v>19.932200000000002</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1526" s="2">
+        <v>25</v>
+      </c>
+      <c r="B1526" s="2">
+        <v>9882000587</v>
+      </c>
+      <c r="C1526" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1526" s="2">
+        <v>988200012</v>
+      </c>
+      <c r="E1526" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1526" s="3">
+        <v>46264</v>
+      </c>
+      <c r="G1526" s="2">
+        <v>68.37</v>
+      </c>
+      <c r="H1526" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1526" s="2">
+        <v>68.37</v>
+      </c>
+      <c r="J1526" s="6">
+        <f t="shared" si="47"/>
+        <v>64.267799999999994</v>
+      </c>
+      <c r="K1526"/>
+      <c r="L1526" s="6">
+        <f t="shared" si="46"/>
+        <v>64.267799999999994</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1527" s="2">
+        <v>26</v>
+      </c>
+      <c r="B1527" s="2">
+        <v>9672033899</v>
+      </c>
+      <c r="C1527" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1527" s="2">
+        <v>202620524</v>
+      </c>
+      <c r="E1527" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1527" s="3">
+        <v>46265</v>
+      </c>
+      <c r="G1527" s="2">
+        <v>120.41</v>
+      </c>
+      <c r="H1527" s="2">
+        <v>18.061</v>
+      </c>
+      <c r="I1527" s="2">
+        <v>102.349</v>
+      </c>
+      <c r="J1527" s="6">
+        <f t="shared" si="47"/>
+        <v>95.12439999999998</v>
+      </c>
+      <c r="K1527"/>
+      <c r="L1527" s="6">
+        <f t="shared" si="46"/>
+        <v>95.12439999999998</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1528" s="2">
+        <v>27</v>
+      </c>
+      <c r="B1528" s="2">
+        <v>9552017225</v>
+      </c>
+      <c r="C1528" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1528" s="2">
+        <v>955201754</v>
+      </c>
+      <c r="E1528" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1528" s="3">
+        <v>46265</v>
+      </c>
+      <c r="G1528" s="2">
+        <v>52.73</v>
+      </c>
+      <c r="H1528" s="2">
+        <v>7.9089999999999998</v>
+      </c>
+      <c r="I1528" s="2">
+        <v>44.820999999999998</v>
+      </c>
+      <c r="J1528" s="6">
+        <f t="shared" si="47"/>
+        <v>41.657199999999996</v>
+      </c>
+      <c r="K1528"/>
+      <c r="L1528" s="6">
+        <f t="shared" si="46"/>
+        <v>41.657199999999996</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1529" s="2">
+        <v>28</v>
+      </c>
+      <c r="B1529" s="2">
+        <v>9771047773</v>
+      </c>
+      <c r="C1529" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1529" s="2">
+        <v>9771044</v>
+      </c>
+      <c r="E1529" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1529" s="3">
+        <v>46265</v>
+      </c>
+      <c r="G1529" s="2">
+        <v>11.08</v>
+      </c>
+      <c r="H1529" s="2">
+        <v>2.2160000000000002</v>
+      </c>
+      <c r="I1529" s="2">
+        <v>8.8640000000000008</v>
+      </c>
+      <c r="J1529" s="6">
+        <f t="shared" si="47"/>
+        <v>8.1991999999999976</v>
+      </c>
+      <c r="K1529"/>
+      <c r="L1529" s="6">
+        <f t="shared" ref="L1529" si="48">J1529-K1529</f>
+        <v>8.1991999999999976</v>
       </c>
     </row>
   </sheetData>
